--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>64.7800594861115</v>
+        <v>10.52675966649312</v>
       </c>
       <c r="D2" t="n">
-        <v>39.5696335941815</v>
+        <v>6.430065459054495</v>
       </c>
       <c r="E2" t="n">
-        <v>30.44545477339555</v>
+        <v>4.947386400676776</v>
       </c>
       <c r="F2" t="n">
-        <v>31.09518546426012</v>
+        <v>5.052967637942269</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.18257034042922</v>
+        <v>3.279667680319748</v>
       </c>
       <c r="D3" t="n">
-        <v>19.83053201505194</v>
+        <v>3.22246145244594</v>
       </c>
       <c r="E3" t="n">
-        <v>30.44545477339555</v>
+        <v>4.947386400676776</v>
       </c>
       <c r="F3" t="n">
-        <v>31.09518546426012</v>
+        <v>5.052967637942269</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>94.24485125923975</v>
+        <v>15.31478832962646</v>
       </c>
       <c r="D4" t="n">
-        <v>93.40937111795378</v>
+        <v>15.17902280666749</v>
       </c>
       <c r="E4" t="n">
-        <v>30.44545477339555</v>
+        <v>4.947386400676776</v>
       </c>
       <c r="F4" t="n">
-        <v>31.09518546426012</v>
+        <v>5.052967637942269</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
